--- a/data/processed/harmonization/Carbon__Soil_organic_carbon_stock/10.15485_2407117/10.15485_2407117_soil_Carbon__Soil_organic_carbon_stock.xlsx
+++ b/data/processed/harmonization/Carbon__Soil_organic_carbon_stock/10.15485_2407117/10.15485_2407117_soil_Carbon__Soil_organic_carbon_stock.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M272"/>
+  <dimension ref="A1:L272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
@@ -440,8 +440,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,11 +501,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>source_row</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -553,10 +547,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -604,10 +595,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -655,10 +643,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -706,10 +691,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -757,10 +739,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -808,10 +787,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -859,10 +835,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -910,10 +883,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -961,10 +931,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1012,10 +979,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1063,10 +1027,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1114,10 +1075,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1165,10 +1123,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1216,10 +1171,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1267,10 +1219,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1318,10 +1267,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1369,10 +1315,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1420,10 +1363,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1471,10 +1411,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1522,10 +1459,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1573,10 +1507,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1624,10 +1555,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1675,10 +1603,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1726,10 +1651,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1777,10 +1699,7 @@
         <v>-148.8504</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1828,10 +1747,7 @@
         <v>-148.851</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1879,10 +1795,7 @@
         <v>-148.851</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1930,10 +1843,7 @@
         <v>-148.851</v>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -1981,10 +1891,7 @@
         <v>-148.851</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2032,10 +1939,7 @@
         <v>-148.851</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2083,10 +1987,7 @@
         <v>-148.851</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2134,10 +2035,7 @@
         <v>-148.851</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2185,10 +2083,7 @@
         <v>-148.851</v>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2236,10 +2131,7 @@
         <v>-148.851</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2287,10 +2179,7 @@
         <v>-148.851</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2338,10 +2227,7 @@
         <v>-148.7576</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2389,10 +2275,7 @@
         <v>-148.7576</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2440,10 +2323,7 @@
         <v>-148.7576</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2491,10 +2371,7 @@
         <v>-148.7576</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2542,10 +2419,7 @@
         <v>-148.7576</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2593,10 +2467,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2644,10 +2515,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2695,10 +2563,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2746,10 +2611,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2797,10 +2659,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2848,10 +2707,7 @@
         <v>-148.7583</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2899,10 +2755,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -2950,10 +2803,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3001,10 +2851,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3052,10 +2899,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3103,10 +2947,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3154,10 +2995,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3205,10 +3043,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3256,10 +3091,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3307,10 +3139,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3358,10 +3187,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3409,10 +3235,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3460,10 +3283,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3511,10 +3331,7 @@
         <v>-148.7643</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3562,10 +3379,7 @@
         <v>-148.762</v>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3613,10 +3427,7 @@
         <v>-148.762</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3664,10 +3475,7 @@
         <v>-148.762</v>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3715,10 +3523,7 @@
         <v>-148.762</v>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3766,10 +3571,7 @@
         <v>-148.762</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3817,10 +3619,7 @@
         <v>-148.762</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3868,10 +3667,7 @@
         <v>-148.762</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3919,10 +3715,7 @@
         <v>-148.762</v>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -3970,10 +3763,7 @@
         <v>-148.762</v>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4021,10 +3811,7 @@
         <v>-148.762</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4072,10 +3859,7 @@
         <v>-148.762</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4123,10 +3907,7 @@
         <v>-148.762</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4174,10 +3955,7 @@
         <v>-148.762</v>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4225,10 +4003,7 @@
         <v>-148.762</v>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4276,10 +4051,7 @@
         <v>-148.762</v>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4327,10 +4099,7 @@
         <v>-148.76</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4378,10 +4147,7 @@
         <v>-148.76</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4429,10 +4195,7 @@
         <v>-148.76</v>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4480,10 +4243,7 @@
         <v>-148.76</v>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4531,10 +4291,7 @@
         <v>-148.76</v>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4582,10 +4339,7 @@
         <v>-148.76</v>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4633,10 +4387,7 @@
         <v>-148.76</v>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4684,10 +4435,7 @@
         <v>-148.76</v>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4735,10 +4483,7 @@
         <v>-148.7582</v>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4786,10 +4531,7 @@
         <v>-148.7582</v>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4837,10 +4579,7 @@
         <v>-148.7582</v>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4888,10 +4627,7 @@
         <v>-148.7582</v>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4939,10 +4675,7 @@
         <v>-148.7582</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -4990,10 +4723,7 @@
         <v>-148.758</v>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5041,10 +4771,7 @@
         <v>-148.758</v>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5092,10 +4819,7 @@
         <v>-148.758</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5143,10 +4867,7 @@
         <v>-148.758</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5194,10 +4915,7 @@
         <v>-148.7584</v>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5245,10 +4963,7 @@
         <v>-148.7584</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5296,10 +5011,7 @@
         <v>-148.758</v>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5347,10 +5059,7 @@
         <v>-148.758</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5398,10 +5107,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5449,10 +5155,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5500,10 +5203,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5551,10 +5251,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5602,10 +5299,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5653,10 +5347,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5704,10 +5395,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5755,10 +5443,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5806,10 +5491,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5857,10 +5539,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5908,10 +5587,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -5959,10 +5635,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6010,10 +5683,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6061,10 +5731,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6112,10 +5779,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6163,10 +5827,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6214,10 +5875,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6265,10 +5923,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6316,10 +5971,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6367,10 +6019,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6418,10 +6067,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6469,10 +6115,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6520,10 +6163,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="L119" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6571,10 +6211,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6622,10 +6259,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="M121" s="2" t="inlineStr">
+      <c r="L121" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6673,10 +6307,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6724,10 +6355,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="M123" s="2" t="inlineStr">
+      <c r="L123" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6775,10 +6403,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6826,10 +6451,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="L125" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6877,10 +6499,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="M126" s="2" t="inlineStr">
+      <c r="L126" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6928,10 +6547,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="L127" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -6979,10 +6595,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="M128" s="2" t="inlineStr">
+      <c r="L128" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7030,10 +6643,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="M129" s="2" t="inlineStr">
+      <c r="L129" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7081,10 +6691,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="L130" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7132,10 +6739,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="M131" s="2" t="inlineStr">
+      <c r="L131" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7183,10 +6787,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
+      <c r="L132" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7234,10 +6835,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="L133" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7285,10 +6883,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7336,10 +6931,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="M135" s="2" t="inlineStr">
+      <c r="L135" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7387,10 +6979,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="L136" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7438,10 +7027,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="M137" s="2" t="inlineStr">
+      <c r="L137" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7489,10 +7075,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="L138" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7540,10 +7123,7 @@
         <v>-148.7572</v>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="L139" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7591,10 +7171,7 @@
         <v>-148.7575</v>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="M140" s="2" t="inlineStr">
+      <c r="L140" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7642,10 +7219,7 @@
         <v>-148.7575</v>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="M141" s="2" t="inlineStr">
+      <c r="L141" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7693,10 +7267,7 @@
         <v>-148.7575</v>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="M142" s="2" t="inlineStr">
+      <c r="L142" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7744,10 +7315,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="M143" s="2" t="inlineStr">
+      <c r="L143" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7795,10 +7363,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="M144" s="2" t="inlineStr">
+      <c r="L144" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7846,10 +7411,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="M145" s="2" t="inlineStr">
+      <c r="L145" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7897,10 +7459,7 @@
         <v>-148.757</v>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="M146" s="2" t="inlineStr">
+      <c r="L146" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7948,10 +7507,7 @@
         <v>-148.757</v>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="M147" s="2" t="inlineStr">
+      <c r="L147" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -7999,10 +7555,7 @@
         <v>-148.757</v>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="M148" s="2" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8050,10 +7603,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="M149" s="2" t="inlineStr">
+      <c r="L149" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8101,10 +7651,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="M150" s="2" t="inlineStr">
+      <c r="L150" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8152,10 +7699,7 @@
         <v>-148.7574</v>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="M151" s="2" t="inlineStr">
+      <c r="L151" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8203,10 +7747,7 @@
         <v>-148.757</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="M152" s="2" t="inlineStr">
+      <c r="L152" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8254,10 +7795,7 @@
         <v>-148.757</v>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="M153" s="2" t="inlineStr">
+      <c r="L153" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8305,10 +7843,7 @@
         <v>-148.757</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="M154" s="2" t="inlineStr">
+      <c r="L154" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8356,10 +7891,7 @@
         <v>-148.852</v>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="M155" s="2" t="inlineStr">
+      <c r="L155" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8407,10 +7939,7 @@
         <v>-148.852</v>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="M156" s="2" t="inlineStr">
+      <c r="L156" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8458,10 +7987,7 @@
         <v>-148.852</v>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="M157" s="2" t="inlineStr">
+      <c r="L157" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8509,10 +8035,7 @@
         <v>-148.852</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="M158" s="2" t="inlineStr">
+      <c r="L158" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8560,10 +8083,7 @@
         <v>-148.852</v>
       </c>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="M159" s="2" t="inlineStr">
+      <c r="L159" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8611,10 +8131,7 @@
         <v>-148.852</v>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="M160" s="2" t="inlineStr">
+      <c r="L160" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8662,10 +8179,7 @@
         <v>-148.852</v>
       </c>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="M161" s="2" t="inlineStr">
+      <c r="L161" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8713,10 +8227,7 @@
         <v>-148.852</v>
       </c>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="M162" s="2" t="inlineStr">
+      <c r="L162" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8764,10 +8275,7 @@
         <v>-148.852</v>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="M163" s="2" t="inlineStr">
+      <c r="L163" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8815,10 +8323,7 @@
         <v>-148.852</v>
       </c>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="L164" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8866,10 +8371,7 @@
         <v>-148.852</v>
       </c>
       <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="L165" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8917,10 +8419,7 @@
         <v>-148.852</v>
       </c>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="M166" s="2" t="inlineStr">
+      <c r="L166" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -8968,10 +8467,7 @@
         <v>-148.852</v>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="M167" s="2" t="inlineStr">
+      <c r="L167" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9019,10 +8515,7 @@
         <v>-148.852</v>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="n">
-        <v>167</v>
-      </c>
-      <c r="M168" s="2" t="inlineStr">
+      <c r="L168" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9070,10 +8563,7 @@
         <v>-148.852</v>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="n">
-        <v>168</v>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="L169" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9121,10 +8611,7 @@
         <v>-148.852</v>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="M170" s="2" t="inlineStr">
+      <c r="L170" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9172,10 +8659,7 @@
         <v>-148.852</v>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="L171" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9223,10 +8707,7 @@
         <v>-148.852</v>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="M172" s="2" t="inlineStr">
+      <c r="L172" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9274,10 +8755,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="L173" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9325,10 +8803,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="M174" s="2" t="inlineStr">
+      <c r="L174" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9376,10 +8851,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="L175" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9427,10 +8899,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="M176" s="2" t="inlineStr">
+      <c r="L176" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9478,10 +8947,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="M177" s="2" t="inlineStr">
+      <c r="L177" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9529,10 +8995,7 @@
         <v>-148.8513</v>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="M178" s="2" t="inlineStr">
+      <c r="L178" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9580,10 +9043,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="M179" s="2" t="inlineStr">
+      <c r="L179" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9631,10 +9091,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="M180" s="2" t="inlineStr">
+      <c r="L180" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9682,10 +9139,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="M181" s="2" t="inlineStr">
+      <c r="L181" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9733,10 +9187,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="M182" s="2" t="inlineStr">
+      <c r="L182" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9784,10 +9235,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="M183" s="2" t="inlineStr">
+      <c r="L183" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9835,10 +9283,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="M184" s="2" t="inlineStr">
+      <c r="L184" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9886,10 +9331,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="M185" s="2" t="inlineStr">
+      <c r="L185" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9937,10 +9379,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="M186" s="2" t="inlineStr">
+      <c r="L186" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -9988,10 +9427,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="M187" s="2" t="inlineStr">
+      <c r="L187" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10039,10 +9475,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="M188" s="2" t="inlineStr">
+      <c r="L188" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10090,10 +9523,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="M189" s="2" t="inlineStr">
+      <c r="L189" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10141,10 +9571,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="M190" s="2" t="inlineStr">
+      <c r="L190" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10192,10 +9619,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="M191" s="2" t="inlineStr">
+      <c r="L191" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10243,10 +9667,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="n">
-        <v>201</v>
-      </c>
-      <c r="M192" s="2" t="inlineStr">
+      <c r="L192" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10294,10 +9715,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="2" t="n">
-        <v>202</v>
-      </c>
-      <c r="M193" s="2" t="inlineStr">
+      <c r="L193" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10345,10 +9763,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="M194" s="2" t="inlineStr">
+      <c r="L194" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10396,10 +9811,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="M195" s="2" t="inlineStr">
+      <c r="L195" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10447,10 +9859,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="M196" s="2" t="inlineStr">
+      <c r="L196" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10498,10 +9907,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="M197" s="2" t="inlineStr">
+      <c r="L197" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10549,10 +9955,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="M198" s="2" t="inlineStr">
+      <c r="L198" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10600,10 +10003,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="M199" s="2" t="inlineStr">
+      <c r="L199" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10651,10 +10051,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="M200" s="2" t="inlineStr">
+      <c r="L200" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10702,10 +10099,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="M201" s="2" t="inlineStr">
+      <c r="L201" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10753,10 +10147,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="M202" s="2" t="inlineStr">
+      <c r="L202" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10804,10 +10195,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="M203" s="2" t="inlineStr">
+      <c r="L203" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10855,10 +10243,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="M204" s="2" t="inlineStr">
+      <c r="L204" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10906,10 +10291,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="M205" s="2" t="inlineStr">
+      <c r="L205" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -10957,10 +10339,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="M206" s="2" t="inlineStr">
+      <c r="L206" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11008,10 +10387,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="M207" s="2" t="inlineStr">
+      <c r="L207" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11059,10 +10435,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="M208" s="2" t="inlineStr">
+      <c r="L208" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11110,10 +10483,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="n">
-        <v>218</v>
-      </c>
-      <c r="M209" s="2" t="inlineStr">
+      <c r="L209" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11161,10 +10531,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="M210" s="2" t="inlineStr">
+      <c r="L210" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11212,10 +10579,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="M211" s="2" t="inlineStr">
+      <c r="L211" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11263,10 +10627,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="n">
-        <v>221</v>
-      </c>
-      <c r="M212" s="2" t="inlineStr">
+      <c r="L212" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11314,10 +10675,7 @@
         <v>-148.8506</v>
       </c>
       <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="M213" s="2" t="inlineStr">
+      <c r="L213" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11365,10 +10723,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="2" t="n">
-        <v>223</v>
-      </c>
-      <c r="M214" s="2" t="inlineStr">
+      <c r="L214" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11416,10 +10771,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="M215" s="2" t="inlineStr">
+      <c r="L215" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11467,10 +10819,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="M216" s="2" t="inlineStr">
+      <c r="L216" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11518,10 +10867,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="2" t="n">
-        <v>226</v>
-      </c>
-      <c r="M217" s="2" t="inlineStr">
+      <c r="L217" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11569,10 +10915,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="n">
-        <v>227</v>
-      </c>
-      <c r="M218" s="2" t="inlineStr">
+      <c r="L218" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11620,10 +10963,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="2" t="n">
-        <v>228</v>
-      </c>
-      <c r="M219" s="2" t="inlineStr">
+      <c r="L219" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11671,10 +11011,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="n">
-        <v>229</v>
-      </c>
-      <c r="M220" s="2" t="inlineStr">
+      <c r="L220" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11722,10 +11059,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="M221" s="2" t="inlineStr">
+      <c r="L221" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11773,10 +11107,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="n">
-        <v>231</v>
-      </c>
-      <c r="M222" s="2" t="inlineStr">
+      <c r="L222" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11824,10 +11155,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="M223" s="2" t="inlineStr">
+      <c r="L223" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11875,10 +11203,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="M224" s="2" t="inlineStr">
+      <c r="L224" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11926,10 +11251,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="M225" s="2" t="inlineStr">
+      <c r="L225" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -11977,10 +11299,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="2" t="n">
-        <v>235</v>
-      </c>
-      <c r="M226" s="2" t="inlineStr">
+      <c r="L226" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -12028,10 +11347,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="n">
-        <v>236</v>
-      </c>
-      <c r="M227" s="2" t="inlineStr">
+      <c r="L227" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -12079,10 +11395,7 @@
         <v>-148.8522</v>
       </c>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="n">
-        <v>237</v>
-      </c>
-      <c r="M228" s="2" t="inlineStr">
+      <c r="L228" s="2" t="inlineStr">
         <is>
           <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (per-sample columns latitude_dd, longitude_dd); source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
@@ -12101,12 +11414,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Summit:50</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12130,12 +11443,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M229" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12152,12 +11462,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Shoulder:50</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12181,12 +11491,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K230" s="2" t="inlineStr"/>
-      <c r="L230" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12203,12 +11510,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Upper Backslope:50</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12232,12 +11539,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12254,12 +11558,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Lower Backslope:50</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12283,12 +11587,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M232" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12305,12 +11606,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Footslope:50</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12334,12 +11635,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12356,12 +11654,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Toeslope:50</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12385,12 +11683,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M234" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12407,12 +11702,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Basin:50</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12436,12 +11731,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M235" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12458,12 +11750,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Summit:50</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12487,12 +11779,9 @@
         <v>-148.759</v>
       </c>
       <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M236" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12509,12 +11798,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Shoulder:50</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12538,12 +11827,9 @@
         <v>-148.759</v>
       </c>
       <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M237" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12560,12 +11846,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Upper Backslope:50</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12589,12 +11875,9 @@
         <v>-148.759</v>
       </c>
       <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M238" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12611,12 +11894,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Lower Backslope:50</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12640,12 +11923,9 @@
         <v>-148.759</v>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12662,12 +11942,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Footslope:50</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12691,12 +11971,9 @@
         <v>-148.759</v>
       </c>
       <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M240" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12713,12 +11990,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Toeslope:50</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12742,12 +12019,9 @@
         <v>-148.759</v>
       </c>
       <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12038,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Basin:50</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12793,12 +12067,9 @@
         <v>-148.759</v>
       </c>
       <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M242" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12815,12 +12086,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Summit:100</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12844,12 +12115,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12866,12 +12134,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Shoulder:100</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12895,12 +12163,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M244" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12917,12 +12182,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Upper Backslope:100</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12946,12 +12211,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -12968,12 +12230,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Lower Backslope:100</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12997,12 +12259,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K246" s="2" t="inlineStr"/>
-      <c r="L246" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13019,12 +12278,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Footslope:100</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13048,12 +12307,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13070,12 +12326,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Toeslope:100</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13099,12 +12355,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K248" s="2" t="inlineStr"/>
-      <c r="L248" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M248" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13121,12 +12374,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Basin:100</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13150,12 +12403,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K249" s="2" t="inlineStr"/>
-      <c r="L249" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13172,12 +12422,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Summit:100</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13201,12 +12451,9 @@
         <v>-148.759</v>
       </c>
       <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13223,12 +12470,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Shoulder:100</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13252,12 +12499,9 @@
         <v>-148.759</v>
       </c>
       <c r="K251" s="2" t="inlineStr"/>
-      <c r="L251" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="M251" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13274,12 +12518,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Upper Backslope:100</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13303,12 +12547,9 @@
         <v>-148.759</v>
       </c>
       <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="M252" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13325,12 +12566,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Lower Backslope:100</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13354,12 +12595,9 @@
         <v>-148.759</v>
       </c>
       <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M253" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13376,12 +12614,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Footslope:100</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13405,12 +12643,9 @@
         <v>-148.759</v>
       </c>
       <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="M254" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13427,12 +12662,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Toeslope:100</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13456,12 +12691,9 @@
         <v>-148.759</v>
       </c>
       <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="M255" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13478,12 +12710,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Basin:100</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13507,12 +12739,9 @@
         <v>-148.759</v>
       </c>
       <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13529,12 +12758,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Lower Backslope:150</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13558,12 +12787,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K257" s="2" t="inlineStr"/>
-      <c r="L257" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13580,12 +12806,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Footslope:150</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13609,12 +12835,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K258" s="2" t="inlineStr"/>
-      <c r="L258" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M258" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13631,12 +12854,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Toeslope:150</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13660,12 +12883,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="M259" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13682,12 +12902,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Basin:150</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13711,12 +12931,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M260" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13733,12 +12950,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Summit:150</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13762,12 +12979,9 @@
         <v>-148.759</v>
       </c>
       <c r="K261" s="2" t="inlineStr"/>
-      <c r="L261" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="M261" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13784,12 +12998,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Shoulder:150</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13813,12 +13027,9 @@
         <v>-148.759</v>
       </c>
       <c r="K262" s="2" t="inlineStr"/>
-      <c r="L262" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="M262" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13046,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Lower Backslope:150</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13864,12 +13075,9 @@
         <v>-148.759</v>
       </c>
       <c r="K263" s="2" t="inlineStr"/>
-      <c r="L263" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="M263" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13886,12 +13094,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Footslope:150</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -13915,12 +13123,9 @@
         <v>-148.759</v>
       </c>
       <c r="K264" s="2" t="inlineStr"/>
-      <c r="L264" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="M264" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13937,12 +13142,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Toeslope:150</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -13966,12 +13171,9 @@
         <v>-148.759</v>
       </c>
       <c r="K265" s="2" t="inlineStr"/>
-      <c r="L265" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="M265" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -13988,12 +13190,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Basin:150</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14017,12 +13219,9 @@
         <v>-148.759</v>
       </c>
       <c r="K266" s="2" t="inlineStr"/>
-      <c r="L266" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M266" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14039,12 +13238,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Lower Backslope:200</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14068,12 +13267,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K267" s="2" t="inlineStr"/>
-      <c r="L267" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="M267" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14090,12 +13286,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Footslope:200</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14119,12 +13315,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K268" s="2" t="inlineStr"/>
-      <c r="L268" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M268" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14141,12 +13334,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Toeslope:200</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14170,12 +13363,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="M269" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14192,12 +13382,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Basin:200</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14221,12 +13411,9 @@
         <v>-148.8511</v>
       </c>
       <c r="K270" s="2" t="inlineStr"/>
-      <c r="L270" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="M270" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14243,12 +13430,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:200</t>
+          <t>Sagwon Hills:Basin:200</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14272,12 +13459,9 @@
         <v>-148.759</v>
       </c>
       <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M271" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -14294,12 +13478,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:300</t>
+          <t>Sagwon Hills:Basin:300</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14323,12 +13507,9 @@
         <v>-148.759</v>
       </c>
       <c r="K272" s="2" t="inlineStr"/>
-      <c r="L272" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="M272" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
